--- a/docs/result/row-data/2nd-test/pub-sub/pub-sub-lock-800-ngrinder-result.xlsx
+++ b/docs/result/row-data/2nd-test/pub-sub/pub-sub-lock-800-ngrinder-result.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{FE7FC8E8-0B20-3940-98C6-3B30389C9C5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14700" yWindow="660" windowWidth="14700" windowHeight="18460" xr2:uid="{0CAA6A65-C174-B043-91C7-F4D87FEE2F3B}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{0CAA6A65-C174-B043-91C7-F4D87FEE2F3B}"/>
   </bookViews>
   <sheets>
     <sheet name="pub-sub-lock-800-ngrinder-resul" sheetId="1" r:id="rId1"/>
@@ -79,7 +79,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="178" formatCode="yyyy/m/d\ h:mm:s"/>
+    <numFmt numFmtId="176" formatCode="yyyy/m/d\ h:mm:s"/>
   </numFmts>
   <fonts count="19">
     <font>
@@ -671,7 +671,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -742,8 +742,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="453907" cy="345992"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="2" name="TextBox 1">
@@ -859,7 +859,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="2" name="TextBox 1">
@@ -927,8 +927,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1049454" cy="359009"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="TextBox 2">
@@ -1097,7 +1097,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="TextBox 2">
@@ -1165,8 +1165,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="806503" cy="359009"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="4" name="TextBox 3">
@@ -1304,7 +1304,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="4" name="TextBox 3">
@@ -1372,8 +1372,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="254000" cy="345800"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="5" name="TextBox 4">
@@ -1458,7 +1458,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="5" name="TextBox 4">
@@ -1526,8 +1526,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="254000" cy="345800"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="6" name="TextBox 5">
@@ -1612,7 +1612,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="6" name="TextBox 5">
@@ -1680,8 +1680,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="177800" cy="345800"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="7" name="TextBox 6">
@@ -1766,7 +1766,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="7" name="TextBox 6">
@@ -1834,8 +1834,8 @@
       <xdr:rowOff>226785</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1303947" cy="498929"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="8" name="TextBox 7">
@@ -2126,7 +2126,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="8" name="TextBox 7">
@@ -2194,8 +2194,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="241300" cy="527004"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="9" name="TextBox 8">
@@ -2291,7 +2291,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="9" name="TextBox 8">
@@ -2362,8 +2362,8 @@
       <xdr:rowOff>226785</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="253787" cy="527324"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="10" name="TextBox 9">
@@ -2459,7 +2459,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="10" name="TextBox 9">
@@ -2530,8 +2530,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1056379" cy="281214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="11" name="TextBox 10">
@@ -2739,7 +2739,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="11" name="TextBox 10">
@@ -2825,8 +2825,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="726930" cy="264885"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="12" name="TextBox 11">
@@ -2972,7 +2972,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="12" name="TextBox 11">
@@ -3043,8 +3043,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1014380" cy="244929"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="13" name="TextBox 12">
@@ -3240,7 +3240,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="13" name="TextBox 12">
@@ -3308,8 +3308,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1759858" cy="498929"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="14" name="TextBox 13">
@@ -3665,7 +3665,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="14" name="TextBox 13">
@@ -3733,8 +3733,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2239972" cy="248557"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="15" name="TextBox 14">
@@ -3957,7 +3957,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="15" name="TextBox 14">
@@ -4025,8 +4025,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1559722" cy="553357"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="16" name="TextBox 15">
@@ -4241,7 +4241,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="16" name="TextBox 15">
@@ -4309,8 +4309,8 @@
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1559722" cy="453572"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="17" name="TextBox 16">
@@ -4502,7 +4502,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="17" name="TextBox 16">
@@ -4570,8 +4570,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2071786" cy="182999"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="18" name="TextBox 17">
@@ -4726,7 +4726,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="18" name="TextBox 17">
